--- a/artfynd/A 60295-2022 artfynd.xlsx
+++ b/artfynd/A 60295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,123 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125900474</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58475</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100017</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klockgroda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bombina bombina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ensligheten, Ensligheten, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>417384</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6146096</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ystad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Balkåkra</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Måns Offerlind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Måns Offerlind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60295-2022 artfynd.xlsx
+++ b/artfynd/A 60295-2022 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>125900474</v>
       </c>
       <c r="B4" t="n">
-        <v>58475</v>
+        <v>58476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60295-2022 artfynd.xlsx
+++ b/artfynd/A 60295-2022 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>125900474</v>
       </c>
       <c r="B4" t="n">
-        <v>58476</v>
+        <v>58477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60295-2022 artfynd.xlsx
+++ b/artfynd/A 60295-2022 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>125900474</v>
       </c>
       <c r="B4" t="n">
-        <v>58477</v>
+        <v>58481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60295-2022 artfynd.xlsx
+++ b/artfynd/A 60295-2022 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>125900474</v>
       </c>
       <c r="B4" t="n">
-        <v>58481</v>
+        <v>58484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60295-2022 artfynd.xlsx
+++ b/artfynd/A 60295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116447452</v>
+        <v>109125301</v>
       </c>
       <c r="B2" t="n">
-        <v>58083</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100118</v>
+        <v>100017</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Klockgroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelophylax esculentus</t>
+          <t>Bombina bombina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +703,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -721,17 +716,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ensligheten (Ensligheten), Sk</t>
+          <t>Ensligheten, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417424</v>
+        <v>417332</v>
       </c>
       <c r="R2" t="n">
-        <v>6146083</v>
+        <v>6146107</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera spelande hannar.</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,12 +795,7 @@
         <v>116447117</v>
       </c>
       <c r="B3" t="n">
-        <v>58098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,7 +828,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ensligheten (Ensligheten), Sk</t>
+          <t>Ensligheten, Ensligheten, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -927,7 +912,7 @@
         <v>125900474</v>
       </c>
       <c r="B4" t="n">
-        <v>58484</v>
+        <v>58786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,6 +1023,241 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109125470</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58810</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100118</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ätlig groda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pelophylax esculentus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ensligheten, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>417332</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6146107</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ystad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Balkåkra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Måns Offerlind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Måns Offerlind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116447452</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58810</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100118</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ätlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pelophylax esculentus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ensligheten, Ensligheten, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>417424</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6146083</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ystad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Balkåkra</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera spelande hannar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Måns Offerlind</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Måns Offerlind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60295-2022 artfynd.xlsx
+++ b/artfynd/A 60295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109125301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116447117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125900474</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109125470</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,8 +1283,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116447452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>